--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964A865B-48EC-4ECB-B247-5507F07036A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7814E012-7DEE-4F21-8D86-DF8BA1829C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -169,9 +169,6 @@
     <t>night</t>
   </si>
   <si>
-    <t>end_game</t>
-  </si>
-  <si>
     <t>≥</t>
   </si>
   <si>
@@ -594,6 +591,9 @@
       <t>.png</t>
     </r>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>endgame</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" s="22">
         <v>1000</v>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="K2" s="22"/>
       <c r="L2" s="22" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M2" s="21"/>
       <c r="N2" s="22"/>
@@ -1397,7 +1397,7 @@
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="L2" xr:uid="{CB93CAC9-E05A-42CD-BF51-C2A084B5D84B}">
-      <formula1>"clinic,night,end_game"</formula1>
+      <formula1>"clinic,night,endgame"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E2 G2" xr:uid="{EEAB203E-6BC2-440A-AE17-A1B685A828E0}">
       <formula1>"≥,≤"</formula1>
@@ -1464,10 +1464,10 @@
       <c r="E2" s="27"/>
       <c r="F2" s="27"/>
       <c r="G2" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1483,7 +1483,7 @@
       <c r="F3" s="27"/>
       <c r="G3" s="27"/>
       <c r="H3" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="54">
@@ -1499,7 +1499,7 @@
       <c r="F4" s="27"/>
       <c r="G4" s="27"/>
       <c r="H4" s="30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7814E012-7DEE-4F21-8D86-DF8BA1829C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E022DD8-2F40-4EEE-B8C6-2ABA74893820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14288" yWindow="3697" windowWidth="12060" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -846,7 +833,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1057,7 +1044,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -1075,7 +1062,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="20" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>11</v>
       </c>
@@ -1137,7 +1124,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="20" customFormat="1">
       <c r="A2" s="24" t="s">
         <v>29</v>
       </c>
@@ -1396,14 +1383,14 @@
     <dataValidation type="list" sqref="S2:S10" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2" xr:uid="{CB93CAC9-E05A-42CD-BF51-C2A084B5D84B}">
-      <formula1>"clinic,night,endgame"</formula1>
-    </dataValidation>
     <dataValidation type="list" sqref="E2 G2" xr:uid="{EEAB203E-6BC2-440A-AE17-A1B685A828E0}">
       <formula1>"≥,≤"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="C2" xr:uid="{6ECE54C8-5545-4B8F-B19D-F059532E0477}">
       <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{D9106D57-6567-45D3-92E1-4F60B09EFED9}">
+      <formula1>"clinic,night,gameover,endgame"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E022DD8-2F40-4EEE-B8C6-2ABA74893820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DD8B03-6661-4189-B650-1E9735A26909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14288" yWindow="3697" windowWidth="12060" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>

--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DD8B03-6661-4189-B650-1E9735A26909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB72B40-6743-4D3A-B8D1-96848434287B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2745" yWindow="5805" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>LineIndex</t>
   </si>
@@ -581,6 +594,10 @@
   </si>
   <si>
     <t>endgame</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -741,7 +758,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -831,9 +848,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1044,7 +1064,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -1062,7 +1082,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1">
+    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
         <v>11</v>
       </c>
@@ -1124,7 +1144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1">
+    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A2" s="24" t="s">
         <v>29</v>
       </c>
@@ -1399,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
@@ -1413,7 +1433,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1438,8 +1458,11 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1456,8 +1479,9 @@
       <c r="H2" s="29" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="26"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1472,8 +1496,9 @@
       <c r="H3" s="27" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="54">
+      <c r="I3" s="26"/>
+    </row>
+    <row r="4" spans="1:9" ht="54">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1488,8 +1513,9 @@
       <c r="H4" s="30" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="26"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1498,8 +1524,9 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="26"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1508,8 +1535,9 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="26"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1518,6 +1546,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
+      <c r="I7" s="27"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>

--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB72B40-6743-4D3A-B8D1-96848434287B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D17A20-A16D-4E7B-9B02-AB7272F76675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2745" yWindow="5805" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -547,6 +534,13 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
+    <t>endgame</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
     <r>
       <t>res://Assets/Background/00</t>
     </r>
@@ -568,7 +562,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>/00</t>
+      <t>/000_0</t>
     </r>
     <r>
       <rPr>
@@ -590,13 +584,6 @@
       </rPr>
       <t>.png</t>
     </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>endgame</t>
-  </si>
-  <si>
-    <t>Music</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -853,7 +840,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1064,7 +1051,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -1082,7 +1069,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="20" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>11</v>
       </c>
@@ -1144,7 +1131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="20" customFormat="1">
       <c r="A2" s="24" t="s">
         <v>29</v>
       </c>
@@ -1169,7 +1156,7 @@
       </c>
       <c r="K2" s="22"/>
       <c r="L2" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M2" s="21"/>
       <c r="N2" s="22"/>
@@ -1459,7 +1446,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1474,7 +1461,7 @@
       <c r="E2" s="27"/>
       <c r="F2" s="27"/>
       <c r="G2" s="28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H2" s="29" t="s">
         <v>34</v>

--- a/DataTables/DetailText/剧情/000_05结局.xlsx
+++ b/DataTables/DetailText/剧情/000_05结局.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D17A20-A16D-4E7B-9B02-AB7272F76675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E6DDED-846C-43BD-8D3A-6E93228BB24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -160,82 +173,6 @@
   </si>
   <si>
     <r>
-      <t>万</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>历</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>二十一年李</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>东</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>壁病逝，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>终</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>年76</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>岁…</t>
-    </r>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -585,6 +522,82 @@
       <t>.png</t>
     </r>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>万</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>历</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二十一年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>李东璧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>病逝，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>终</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岁…</t>
+    </r>
+    <phoneticPr fontId="9"/>
   </si>
 </sst>
 </file>
@@ -840,7 +853,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1051,7 +1064,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -1069,7 +1082,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1">
+    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
         <v>11</v>
       </c>
@@ -1131,7 +1144,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1">
+    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A2" s="24" t="s">
         <v>29</v>
       </c>
@@ -1156,7 +1169,7 @@
       </c>
       <c r="K2" s="22"/>
       <c r="L2" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M2" s="21"/>
       <c r="N2" s="22"/>
@@ -1446,7 +1459,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1461,10 +1474,10 @@
       <c r="E2" s="27"/>
       <c r="F2" s="27"/>
       <c r="G2" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="29" t="s">
         <v>39</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>34</v>
       </c>
       <c r="I2" s="26"/>
     </row>
@@ -1481,7 +1494,7 @@
       <c r="F3" s="27"/>
       <c r="G3" s="27"/>
       <c r="H3" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I3" s="26"/>
     </row>
@@ -1498,7 +1511,7 @@
       <c r="F4" s="27"/>
       <c r="G4" s="27"/>
       <c r="H4" s="30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I4" s="26"/>
     </row>
